--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2021_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2021_antofagasta.xlsx
@@ -532,7 +532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -541,20 +541,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>485513.38</v>
+          <t>María Elena</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,42 +555,33 @@
           <t>Calama</t>
         </is>
       </c>
-      <c r="B3">
-        <v>502491.59</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Tocopilla</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mejillones</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>421862.59</v>
+          <t>Antofagasta</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
+          <t>Mejillones</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>265143.56</v>
+          <t>Taltal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -607,28 +590,19 @@
           <t>Sierra Gorda</t>
         </is>
       </c>
-      <c r="B8">
-        <v>433584.34</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Taltal</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>311181.94</v>
+          <t>San Pedro de Atacama</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>336201.97</v>
+          <t>Ollagüe</t>
+        </is>
       </c>
     </row>
   </sheetData>
